--- a/inputs/data_symbols_TD/08_LTAN06_800km_1213COLD_PY_ALL_HEAT_PY_0p5.xlsx
+++ b/inputs/data_symbols_TD/08_LTAN06_800km_1213COLD_PY_ALL_HEAT_PY_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAFE12AE-7255-4EC5-8D22-FE4F84106E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB651092-641E-490E-BCC8-0A8AEF7DF925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{2338A771-D7D2-4E0D-86A3-E9CF0D22ECD2}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{579DD63A-BB7C-43BE-B9EA-8B3F95FAF2C8}"/>
   </bookViews>
   <sheets>
     <sheet name="08_LTAN06_800km_1213COLD_PY_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F88CD7E-A154-419C-9FA7-17E401B3CF13}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43E5C071-425E-42A4-AE6B-F97DDC813B8F}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>14.56568</v>
+        <v>40.35998</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>14.56568</v>
+        <v>40.35998</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>14.568429999999999</v>
+        <v>40.369259999999997</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>14.57554</v>
+        <v>40.393360000000001</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>14.585240000000001</v>
+        <v>40.42651</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>14.596539999999999</v>
+        <v>40.465510000000002</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>14.60886</v>
+        <v>40.508499999999998</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>14.621840000000001</v>
+        <v>40.554369999999999</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -1143,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>14.635260000000001</v>
+        <v>40.602420000000002</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>14.648960000000001</v>
+        <v>40.652200000000001</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -1171,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>14.66283</v>
+        <v>40.703380000000003</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>14.676769999999999</v>
+        <v>40.755699999999997</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>14.6907</v>
+        <v>40.808909999999997</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>14.704560000000001</v>
+        <v>40.862830000000002</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>14.71829</v>
+        <v>40.917319999999997</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>14.73184</v>
+        <v>40.972270000000002</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>14.74516</v>
+        <v>41.02758</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
@@ -1269,7 +1269,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>14.75821</v>
+        <v>41.083109999999998</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>14.770949999999999</v>
+        <v>41.138770000000001</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
@@ -1297,7 +1297,7 @@
         <v>3</v>
       </c>
       <c r="D21">
-        <v>14.7659</v>
+        <v>41.135950000000001</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
@@ -1311,7 +1311,7 @@
         <v>3</v>
       </c>
       <c r="D22">
-        <v>14.73255</v>
+        <v>41.03989</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
@@ -1325,7 +1325,7 @@
         <v>3</v>
       </c>
       <c r="D23">
-        <v>14.681649999999999</v>
+        <v>40.8874</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
@@ -1339,7 +1339,7 @@
         <v>3</v>
       </c>
       <c r="D24">
-        <v>14.619149999999999</v>
+        <v>40.698860000000003</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
@@ -1353,7 +1353,7 @@
         <v>3</v>
       </c>
       <c r="D25">
-        <v>14.54853</v>
+        <v>40.4861</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="D26">
-        <v>14.47189</v>
+        <v>40.256369999999997</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
@@ -1381,7 +1381,7 @@
         <v>3</v>
       </c>
       <c r="D27">
-        <v>14.39059</v>
+        <v>40.014299999999999</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
@@ -1395,7 +1395,7 @@
         <v>3</v>
       </c>
       <c r="D28">
-        <v>14.30556</v>
+        <v>39.763039999999997</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
@@ -1409,7 +1409,7 @@
         <v>3</v>
       </c>
       <c r="D29">
-        <v>14.217460000000001</v>
+        <v>39.504820000000002</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
@@ -1423,7 +1423,7 @@
         <v>3</v>
       </c>
       <c r="D30">
-        <v>14.12683</v>
+        <v>39.241309999999999</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
@@ -1437,7 +1437,7 @@
         <v>3</v>
       </c>
       <c r="D31">
-        <v>14.034039999999999</v>
+        <v>38.97381</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
@@ -1451,7 +1451,7 @@
         <v>3</v>
       </c>
       <c r="D32">
-        <v>13.939439999999999</v>
+        <v>38.703319999999998</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
@@ -1465,7 +1465,7 @@
         <v>3</v>
       </c>
       <c r="D33">
-        <v>13.84328</v>
+        <v>38.430579999999999</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
@@ -1479,7 +1479,7 @@
         <v>3</v>
       </c>
       <c r="D34">
-        <v>13.745799999999999</v>
+        <v>38.156219999999998</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
@@ -1493,7 +1493,7 @@
         <v>3</v>
       </c>
       <c r="D35">
-        <v>13.647180000000001</v>
+        <v>37.880719999999997</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.4">
@@ -1507,7 +1507,7 @@
         <v>3</v>
       </c>
       <c r="D36">
-        <v>13.547599999999999</v>
+        <v>37.604489999999998</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
@@ -1521,7 +1521,7 @@
         <v>3</v>
       </c>
       <c r="D37">
-        <v>13.44721</v>
+        <v>37.327930000000002</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>13.363530000000001</v>
+        <v>37.109400000000001</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.4">
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>13.30714</v>
+        <v>36.98359</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.4">
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>13.26741</v>
+        <v>36.91422</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.4">
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>13.238440000000001</v>
+        <v>36.8812</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.4">
@@ -1591,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>13.21687</v>
+        <v>36.87285</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.4">
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>13.20064</v>
+        <v>36.88205</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.4">
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>13.188470000000001</v>
+        <v>36.904220000000002</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.4">
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>13.17947</v>
+        <v>36.936259999999997</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.4">
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>13.173019999999999</v>
+        <v>36.975940000000001</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.4">
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>13.168659999999999</v>
+        <v>37.021599999999999</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.4">
@@ -1675,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>13.16605</v>
+        <v>37.071930000000002</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.4">
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>13.164899999999999</v>
+        <v>37.125880000000002</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.4">
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>13.165010000000001</v>
+        <v>37.182639999999999</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.4">
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>13.16621</v>
+        <v>37.241509999999998</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.4">
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>13.168369999999999</v>
+        <v>37.301960000000001</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.4">
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>13.171390000000001</v>
+        <v>37.363549999999996</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.4">
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>13.175179999999999</v>
+        <v>37.425919999999998</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.4">
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>13.1797</v>
+        <v>37.48883</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.4">
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>13.18488</v>
+        <v>37.552030000000002</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.4">
@@ -1801,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>13.19069</v>
+        <v>37.615340000000003</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.4">
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>13.197089999999999</v>
+        <v>37.678579999999997</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.4">
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>13.204050000000001</v>
+        <v>37.741610000000001</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.4">
@@ -1843,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>13.211550000000001</v>
+        <v>37.804310000000001</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.4">
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>13.219580000000001</v>
+        <v>37.866579999999999</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.4">
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>13.22813</v>
+        <v>37.928359999999998</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.4">
@@ -1885,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>13.237209999999999</v>
+        <v>37.989559999999997</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.4">
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>13.246829999999999</v>
+        <v>38.050150000000002</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.4">
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>13.257</v>
+        <v>38.110149999999997</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.4">
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>13.267749999999999</v>
+        <v>38.16957</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.4">
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>13.279120000000001</v>
+        <v>38.228470000000002</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.4">
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>13.291130000000001</v>
+        <v>38.286879999999996</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.4">
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>13.30383</v>
+        <v>38.344850000000001</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.4">
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>13.317259999999999</v>
+        <v>38.402439999999999</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.4">
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>13.33146</v>
+        <v>38.459710000000001</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.4">
@@ -2011,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>13.34647</v>
+        <v>38.516730000000003</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.4">
@@ -2025,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>13.36234</v>
+        <v>38.57358</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.4">
@@ -2039,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>13.379110000000001</v>
+        <v>38.630369999999999</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.4">
@@ -2053,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>13.39682</v>
+        <v>38.68721</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.4">
@@ -2067,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>13.415520000000001</v>
+        <v>38.744160000000001</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.4">
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>13.435230000000001</v>
+        <v>38.801299999999998</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.4">
@@ -2095,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>13.45599</v>
+        <v>38.858699999999999</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.4">
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>13.477819999999999</v>
+        <v>38.916409999999999</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.4">
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>13.500730000000001</v>
+        <v>38.974550000000001</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.4">
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>13.52474</v>
+        <v>39.033169999999998</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.4">
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>13.549849999999999</v>
+        <v>39.092329999999997</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.4">
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>13.57605</v>
+        <v>39.152059999999999</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.4">
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>13.60333</v>
+        <v>39.21237</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.4">
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>13.63165</v>
+        <v>39.273310000000002</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.4">
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>13.661</v>
+        <v>39.334910000000001</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.4">
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>13.691330000000001</v>
+        <v>39.397190000000002</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.4">
@@ -2235,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>13.72259</v>
+        <v>39.460129999999999</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.4">
@@ -2249,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>13.754709999999999</v>
+        <v>39.523719999999997</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.4">
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>13.78764</v>
+        <v>39.587899999999998</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.4">
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>13.821300000000001</v>
+        <v>39.652650000000001</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.4">
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>13.855600000000001</v>
+        <v>39.717930000000003</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.4">
@@ -2305,7 +2305,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>13.890470000000001</v>
+        <v>39.783670000000001</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.4">
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>13.92581</v>
+        <v>39.849800000000002</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.4">
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>13.96152</v>
+        <v>39.916249999999998</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.4">
@@ -2347,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>13.99751</v>
+        <v>39.982959999999999</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.4">
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>14.03365</v>
+        <v>40.049889999999998</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.4">
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>14.069850000000001</v>
+        <v>40.116959999999999</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.4">
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>14.106009999999999</v>
+        <v>40.184069999999998</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.4">
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>14.141999999999999</v>
+        <v>40.251100000000001</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.4">
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>14.177759999999999</v>
+        <v>40.317979999999999</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.4">
@@ -2431,7 +2431,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>14.21317</v>
+        <v>40.384650000000001</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.4">
@@ -2445,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>14.248150000000001</v>
+        <v>40.451050000000002</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.4">
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>14.282640000000001</v>
+        <v>40.517099999999999</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.4">
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>14.31654</v>
+        <v>40.582709999999999</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.4">
@@ -2487,7 +2487,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>14.34981</v>
+        <v>40.64781</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.4">
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>14.382389999999999</v>
+        <v>40.712350000000001</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.4">
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>14.414249999999999</v>
+        <v>40.776310000000002</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.4">
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>14.44534</v>
+        <v>40.839680000000001</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.4">
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>14.47566</v>
+        <v>40.902479999999997</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.4">
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>14.50517</v>
+        <v>40.964770000000001</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.4">
@@ -2571,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>14.53387</v>
+        <v>41.02657</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.4">
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>14.56175</v>
+        <v>41.087899999999998</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.4">
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>14.588789999999999</v>
+        <v>41.148719999999997</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.4">
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>14.614979999999999</v>
+        <v>41.209040000000002</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.4">
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>14.640319999999999</v>
+        <v>41.268859999999997</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.4">
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>14.66479</v>
+        <v>41.328209999999999</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.4">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>14.6884</v>
+        <v>41.387070000000001</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.4">
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="D119">
-        <v>14.711130000000001</v>
+        <v>41.445430000000002</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.4">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>14.732989999999999</v>
+        <v>41.503270000000001</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.4">
@@ -2697,7 +2697,7 @@
         <v>3</v>
       </c>
       <c r="D121">
-        <v>14.73653</v>
+        <v>41.502020000000002</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.4">
@@ -2711,7 +2711,7 @@
         <v>3</v>
       </c>
       <c r="D122">
-        <v>14.711259999999999</v>
+        <v>41.406959999999998</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.4">
@@ -2725,7 +2725,7 @@
         <v>3</v>
       </c>
       <c r="D123">
-        <v>14.667960000000001</v>
+        <v>41.255009999999999</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.4">
@@ -2739,7 +2739,7 @@
         <v>3</v>
       </c>
       <c r="D124">
-        <v>14.61261</v>
+        <v>41.066600000000001</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.4">
@@ -2753,7 +2753,7 @@
         <v>3</v>
       </c>
       <c r="D125">
-        <v>14.548719999999999</v>
+        <v>40.853639999999999</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.4">
@@ -2767,7 +2767,7 @@
         <v>3</v>
       </c>
       <c r="D126">
-        <v>14.47841</v>
+        <v>40.62341</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.4">
@@ -2781,7 +2781,7 @@
         <v>3</v>
       </c>
       <c r="D127">
-        <v>14.40307</v>
+        <v>40.380589999999998</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.4">
@@ -2795,7 +2795,7 @@
         <v>3</v>
       </c>
       <c r="D128">
-        <v>14.323639999999999</v>
+        <v>40.128349999999998</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.4">
@@ -2809,7 +2809,7 @@
         <v>3</v>
       </c>
       <c r="D129">
-        <v>14.240819999999999</v>
+        <v>39.868969999999997</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.4">
@@ -2823,7 +2823,7 @@
         <v>3</v>
       </c>
       <c r="D130">
-        <v>14.15513</v>
+        <v>39.604140000000001</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.4">
@@ -2837,7 +2837,7 @@
         <v>3</v>
       </c>
       <c r="D131">
-        <v>14.06701</v>
+        <v>39.335169999999998</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.4">
@@ -2851,7 +2851,7 @@
         <v>3</v>
       </c>
       <c r="D132">
-        <v>13.97678</v>
+        <v>39.063090000000003</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.4">
@@ -2865,7 +2865,7 @@
         <v>3</v>
       </c>
       <c r="D133">
-        <v>13.884740000000001</v>
+        <v>38.78866</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.4">
@@ -2879,7 +2879,7 @@
         <v>3</v>
       </c>
       <c r="D134">
-        <v>13.791119999999999</v>
+        <v>38.512520000000002</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.4">
@@ -2893,7 +2893,7 @@
         <v>3</v>
       </c>
       <c r="D135">
-        <v>13.69613</v>
+        <v>38.23516</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.4">
@@ -2907,7 +2907,7 @@
         <v>3</v>
       </c>
       <c r="D136">
-        <v>13.599959999999999</v>
+        <v>37.95702</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.4">
@@ -2921,7 +2921,7 @@
         <v>3</v>
       </c>
       <c r="D137">
-        <v>13.50277</v>
+        <v>37.67848</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.4">
@@ -2935,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="D138">
-        <v>13.422090000000001</v>
+        <v>37.457940000000001</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.4">
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="D139">
-        <v>13.36853</v>
+        <v>37.330120000000001</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.4">
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="D140">
-        <v>13.331429999999999</v>
+        <v>37.258719999999997</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.4">
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="D141">
-        <v>13.30495</v>
+        <v>37.22363</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.4">
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="D142">
-        <v>13.2857</v>
+        <v>37.213189999999997</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.4">
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="D143">
-        <v>13.271649999999999</v>
+        <v>37.220280000000002</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.4">
@@ -3019,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="D144">
-        <v>13.261509999999999</v>
+        <v>37.240319999999997</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.4">
@@ -3033,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="D145">
-        <v>13.25441</v>
+        <v>37.270209999999999</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.4">
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="D146">
-        <v>13.249739999999999</v>
+        <v>37.307720000000003</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.4">
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="D147">
-        <v>13.24704</v>
+        <v>37.351199999999999</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.4">
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="D148">
-        <v>13.245979999999999</v>
+        <v>37.399340000000002</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.4">
@@ -3089,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="D149">
-        <v>13.246270000000001</v>
+        <v>37.45111</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.4">
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="D150">
-        <v>13.247730000000001</v>
+        <v>37.505659999999999</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.4">
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="D151">
-        <v>13.25018</v>
+        <v>37.562330000000003</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.4">
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="D152">
-        <v>13.253489999999999</v>
+        <v>37.620579999999997</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.4">
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="D153">
-        <v>13.25759</v>
+        <v>37.679960000000001</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.4">
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="D154">
-        <v>13.26238</v>
+        <v>37.740139999999997</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.4">
@@ -3173,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="D155">
-        <v>13.26782</v>
+        <v>37.800849999999997</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.4">
@@ -3187,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="D156">
-        <v>13.273860000000001</v>
+        <v>37.86186</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.4">
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="D157">
-        <v>13.28045</v>
+        <v>37.923000000000002</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.4">
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="D158">
-        <v>13.287570000000001</v>
+        <v>37.984070000000003</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.4">
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="D159">
-        <v>13.295199999999999</v>
+        <v>38.044939999999997</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.4">
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="D160">
-        <v>13.30331</v>
+        <v>38.105499999999999</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.4">
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="D161">
-        <v>13.31189</v>
+        <v>38.165649999999999</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.4">
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="D162">
-        <v>13.32095</v>
+        <v>38.22531</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.4">
@@ -3285,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="D163">
-        <v>13.330489999999999</v>
+        <v>38.284410000000001</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.4">
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="D164">
-        <v>13.34052</v>
+        <v>38.342930000000003</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.4">
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="D165">
-        <v>13.35106</v>
+        <v>38.400860000000002</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.4">
@@ -3327,7 +3327,7 @@
         <v>0</v>
       </c>
       <c r="D166">
-        <v>13.36215</v>
+        <v>38.458240000000004</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.4">
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="D167">
-        <v>13.373810000000001</v>
+        <v>38.515120000000003</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.4">
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="D168">
-        <v>13.38608</v>
+        <v>38.57152</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.4">
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="D169">
-        <v>13.399010000000001</v>
+        <v>38.627499999999998</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.4">
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="D170">
-        <v>13.41264</v>
+        <v>38.683129999999998</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.4">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="D171">
-        <v>13.427</v>
+        <v>38.73845</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.4">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="D172">
-        <v>13.44215</v>
+        <v>38.79354</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.4">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="D173">
-        <v>13.458130000000001</v>
+        <v>38.848489999999998</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.4">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="D174">
-        <v>13.47499</v>
+        <v>38.903399999999998</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.4">
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="D175">
-        <v>13.49277</v>
+        <v>38.958379999999998</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.4">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="D176">
-        <v>13.511509999999999</v>
+        <v>39.013489999999997</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.4">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="D177">
-        <v>13.53125</v>
+        <v>39.068809999999999</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.4">
@@ -3495,7 +3495,7 @@
         <v>0</v>
       </c>
       <c r="D178">
-        <v>13.552009999999999</v>
+        <v>39.124400000000001</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.4">
@@ -3509,7 +3509,7 @@
         <v>0</v>
       </c>
       <c r="D179">
-        <v>13.573829999999999</v>
+        <v>39.180340000000001</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.4">
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="D180">
-        <v>13.59671</v>
+        <v>39.236710000000002</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.4">
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="D181">
-        <v>13.62067</v>
+        <v>39.293599999999998</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.4">
@@ -3551,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="D182">
-        <v>13.645720000000001</v>
+        <v>39.351039999999998</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.4">
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="D183">
-        <v>13.671849999999999</v>
+        <v>39.409059999999997</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.4">
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="D184">
-        <v>13.69904</v>
+        <v>39.467689999999997</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.4">
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="D185">
-        <v>13.727259999999999</v>
+        <v>39.526969999999999</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.4">
@@ -3607,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="D186">
-        <v>13.756500000000001</v>
+        <v>39.586930000000002</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.4">
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="D187">
-        <v>13.7867</v>
+        <v>39.647579999999998</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.4">
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="D188">
-        <v>13.817830000000001</v>
+        <v>39.708919999999999</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.4">
@@ -3649,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="D189">
-        <v>13.8498</v>
+        <v>39.770910000000001</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.4">
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="D190">
-        <v>13.882580000000001</v>
+        <v>39.83352</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.4">
@@ -3677,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="D191">
-        <v>13.916069999999999</v>
+        <v>39.896709999999999</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.4">
@@ -3691,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="D192">
-        <v>13.95021</v>
+        <v>39.960450000000002</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.4">
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="D193">
-        <v>13.9849</v>
+        <v>40.02467</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.4">
@@ -3719,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="D194">
-        <v>14.020049999999999</v>
+        <v>40.089289999999998</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.4">
@@ -3733,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="D195">
-        <v>14.055569999999999</v>
+        <v>40.154249999999998</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.4">
@@ -3747,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="D196">
-        <v>14.09135</v>
+        <v>40.21949</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.4">
@@ -3761,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="D197">
-        <v>14.12729</v>
+        <v>40.284959999999998</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.4">
@@ -3775,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="D198">
-        <v>14.16328</v>
+        <v>40.350580000000001</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.4">
@@ -3789,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="D199">
-        <v>14.199210000000001</v>
+        <v>40.416249999999998</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.4">
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="D200">
-        <v>14.23499</v>
+        <v>40.481870000000001</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.4">
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="D201">
-        <v>14.27051</v>
+        <v>40.547339999999998</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.4">
@@ -3831,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="D202">
-        <v>14.30569</v>
+        <v>40.61262</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.4">
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="D203">
-        <v>14.340439999999999</v>
+        <v>40.677639999999997</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.4">
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="D204">
-        <v>14.374689999999999</v>
+        <v>40.742319999999999</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.4">
@@ -3873,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="D205">
-        <v>14.40835</v>
+        <v>40.806579999999997</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.4">
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="D206">
-        <v>14.441369999999999</v>
+        <v>40.870330000000003</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.4">
@@ -3901,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="D207">
-        <v>14.473699999999999</v>
+        <v>40.933540000000001</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.4">
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="D208">
-        <v>14.50531</v>
+        <v>40.996189999999999</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.4">
@@ -3929,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="D209">
-        <v>14.536149999999999</v>
+        <v>41.058250000000001</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.4">
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="D210">
-        <v>14.5662</v>
+        <v>41.119759999999999</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.4">
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="D211">
-        <v>14.595459999999999</v>
+        <v>41.180770000000003</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.4">
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="D212">
-        <v>14.623900000000001</v>
+        <v>41.241300000000003</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.4">
@@ -3985,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="D213">
-        <v>14.65151</v>
+        <v>41.301360000000003</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.4">
@@ -3999,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="D214">
-        <v>14.678280000000001</v>
+        <v>41.360939999999999</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.4">
@@ -4013,7 +4013,7 @@
         <v>0</v>
       </c>
       <c r="D215">
-        <v>14.70421</v>
+        <v>41.420020000000001</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.4">
@@ -4027,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="D216">
-        <v>14.72927</v>
+        <v>41.478619999999999</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.4">
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="D217">
-        <v>14.75348</v>
+        <v>41.536749999999998</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.4">
@@ -4055,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="D218">
-        <v>14.776820000000001</v>
+        <v>41.594410000000003</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.4">
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="D219">
-        <v>14.79928</v>
+        <v>41.65157</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.4">
@@ -4083,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="D220">
-        <v>14.820869999999999</v>
+        <v>41.70823</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.4">
@@ -4097,7 +4097,7 @@
         <v>3</v>
       </c>
       <c r="D221">
-        <v>14.82413</v>
+        <v>41.70579</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.4">
@@ -4111,7 +4111,7 @@
         <v>3</v>
       </c>
       <c r="D222">
-        <v>14.798590000000001</v>
+        <v>41.609560000000002</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.4">
@@ -4125,7 +4125,7 @@
         <v>3</v>
       </c>
       <c r="D223">
-        <v>14.75501</v>
+        <v>41.456440000000001</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.4">
@@ -4139,7 +4139,7 @@
         <v>3</v>
       </c>
       <c r="D224">
-        <v>14.699389999999999</v>
+        <v>41.26688</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.4">
@@ -4153,7 +4153,7 @@
         <v>3</v>
       </c>
       <c r="D225">
-        <v>14.63522</v>
+        <v>41.052770000000002</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.4">
@@ -4167,7 +4167,7 @@
         <v>3</v>
       </c>
       <c r="D226">
-        <v>14.564640000000001</v>
+        <v>40.82141</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.4">
@@ -4181,7 +4181,7 @@
         <v>3</v>
       </c>
       <c r="D227">
-        <v>14.48902</v>
+        <v>40.577480000000001</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.4">
@@ -4195,7 +4195,7 @@
         <v>3</v>
       </c>
       <c r="D228">
-        <v>14.40931</v>
+        <v>40.32414</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.4">
@@ -4209,7 +4209,7 @@
         <v>3</v>
       </c>
       <c r="D229">
-        <v>14.32621</v>
+        <v>40.063659999999999</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.4">
@@ -4223,7 +4223,7 @@
         <v>3</v>
       </c>
       <c r="D230">
-        <v>14.24025</v>
+        <v>39.797759999999997</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.4">
@@ -4237,7 +4237,7 @@
         <v>3</v>
       </c>
       <c r="D231">
-        <v>14.151859999999999</v>
+        <v>39.527740000000001</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.4">
@@ -4251,7 +4251,7 @@
         <v>3</v>
       </c>
       <c r="D232">
-        <v>14.061360000000001</v>
+        <v>39.25461</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.4">
@@ -4265,7 +4265,7 @@
         <v>3</v>
       </c>
       <c r="D233">
-        <v>13.96904</v>
+        <v>38.979149999999997</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.4">
@@ -4279,7 +4279,7 @@
         <v>3</v>
       </c>
       <c r="D234">
-        <v>13.87515</v>
+        <v>38.701979999999999</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.4">
@@ -4293,7 +4293,7 @@
         <v>3</v>
       </c>
       <c r="D235">
-        <v>13.77989</v>
+        <v>38.42362</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.4">
@@ -4307,7 +4307,7 @@
         <v>3</v>
       </c>
       <c r="D236">
-        <v>13.683450000000001</v>
+        <v>38.144480000000001</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.4">
@@ -4321,7 +4321,7 @@
         <v>3</v>
       </c>
       <c r="D237">
-        <v>13.585990000000001</v>
+        <v>37.864960000000004</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.4">
@@ -4335,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="D238">
-        <v>13.505050000000001</v>
+        <v>37.643459999999997</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.4">
@@ -4349,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="D239">
-        <v>13.451219999999999</v>
+        <v>37.514699999999998</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.4">
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="D240">
-        <v>13.41386</v>
+        <v>37.442360000000001</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.4">
@@ -4377,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="D241">
-        <v>13.387119999999999</v>
+        <v>37.406350000000003</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.4">
@@ -4391,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="D242">
-        <v>13.367599999999999</v>
+        <v>37.39499</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.4">
@@ -4405,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="D243">
-        <v>13.353300000000001</v>
+        <v>37.401179999999997</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.4">
@@ -4419,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="D244">
-        <v>13.3429</v>
+        <v>37.420310000000001</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.4">
@@ -4433,7 +4433,7 @@
         <v>0</v>
       </c>
       <c r="D245">
-        <v>13.33555</v>
+        <v>37.449300000000001</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.4">
@@ -4447,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="D246">
-        <v>13.33062</v>
+        <v>37.485930000000003</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.4">
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="D247">
-        <v>13.327669999999999</v>
+        <v>37.52852</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.4">
@@ -4475,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="D248">
-        <v>13.32634</v>
+        <v>37.575780000000002</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.4">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="D249">
-        <v>13.32639</v>
+        <v>37.626669999999997</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.4">
@@ -4503,7 +4503,7 @@
         <v>0</v>
       </c>
       <c r="D250">
-        <v>13.327590000000001</v>
+        <v>37.68036</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.4">
@@ -4517,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="D251">
-        <v>13.329789999999999</v>
+        <v>37.736159999999998</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.4">
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="D252">
-        <v>13.33286</v>
+        <v>37.79354</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.4">
@@ -4545,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="D253">
-        <v>13.3367</v>
+        <v>37.852069999999998</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.4">
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="D254">
-        <v>13.34125</v>
+        <v>37.911389999999997</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.4">
@@ -4573,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="D255">
-        <v>13.346439999999999</v>
+        <v>37.971249999999998</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.4">
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="D256">
-        <v>13.35223</v>
+        <v>38.03143</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.4">
@@ -4601,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="D257">
-        <v>13.35858</v>
+        <v>38.091720000000002</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.4">
@@ -4615,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="D258">
-        <v>13.365460000000001</v>
+        <v>38.151949999999999</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.4">
@@ -4629,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="D259">
-        <v>13.37284</v>
+        <v>38.212000000000003</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.4">
@@ -4643,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="D260">
-        <v>13.380710000000001</v>
+        <v>38.271729999999998</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.4">
@@ -4657,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="D261">
-        <v>13.389049999999999</v>
+        <v>38.331049999999998</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.4">
@@ -4671,7 +4671,7 @@
         <v>0</v>
       </c>
       <c r="D262">
-        <v>13.397869999999999</v>
+        <v>38.389899999999997</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.4">
@@ -4685,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="D263">
-        <v>13.407170000000001</v>
+        <v>38.448189999999997</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.4">
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="D264">
-        <v>13.41696</v>
+        <v>38.505899999999997</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.4">
@@ -4713,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="D265">
-        <v>13.42727</v>
+        <v>38.563029999999998</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.4">
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="D266">
-        <v>13.43812</v>
+        <v>38.619610000000002</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.4">
@@ -4741,7 +4741,7 @@
         <v>0</v>
       </c>
       <c r="D267">
-        <v>13.44955</v>
+        <v>38.675690000000003</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.4">
@@ -4755,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="D268">
-        <v>13.461589999999999</v>
+        <v>38.731310000000001</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.4">
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="D269">
-        <v>13.47429</v>
+        <v>38.78651</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.4">
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="D270">
-        <v>13.487690000000001</v>
+        <v>38.841349999999998</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.4">
@@ -4797,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="D271">
-        <v>13.50182</v>
+        <v>38.895899999999997</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.4">
@@ -4811,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="D272">
-        <v>13.51675</v>
+        <v>38.950220000000002</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.4">
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="D273">
-        <v>13.532500000000001</v>
+        <v>39.00441</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.4">
@@ -4839,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="D274">
-        <v>13.54914</v>
+        <v>39.05856</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.4">
@@ -4853,7 +4853,7 @@
         <v>0</v>
       </c>
       <c r="D275">
-        <v>13.566689999999999</v>
+        <v>39.112769999999998</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.4">
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="D276">
-        <v>13.58521</v>
+        <v>39.167140000000003</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.4">
@@ -4881,7 +4881,7 @@
         <v>0</v>
       </c>
       <c r="D277">
-        <v>13.60472</v>
+        <v>39.221710000000002</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.4">
@@ -4895,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="D278">
-        <v>13.62527</v>
+        <v>39.276560000000003</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.4">
@@ -4909,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="D279">
-        <v>13.64686</v>
+        <v>39.331760000000003</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.4">
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="D280">
-        <v>13.66952</v>
+        <v>39.3874</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.4">
@@ -4937,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="D281">
-        <v>13.69327</v>
+        <v>39.443559999999998</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.4">
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="D282">
-        <v>13.7181</v>
+        <v>39.500279999999997</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.4">
@@ -4965,7 +4965,7 @@
         <v>0</v>
       </c>
       <c r="D283">
-        <v>13.744009999999999</v>
+        <v>39.557589999999998</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.4">
@@ -4979,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="D284">
-        <v>13.77098</v>
+        <v>39.615499999999997</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.4">
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="D285">
-        <v>13.798999999999999</v>
+        <v>39.67407</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.4">
@@ -5007,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="D286">
-        <v>13.82802</v>
+        <v>39.733319999999999</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.4">
@@ -5021,7 +5021,7 @@
         <v>0</v>
       </c>
       <c r="D287">
-        <v>13.85801</v>
+        <v>39.79327</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.4">
@@ -5035,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="D288">
-        <v>13.888920000000001</v>
+        <v>39.853909999999999</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.4">
@@ -5049,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="D289">
-        <v>13.92069</v>
+        <v>39.915210000000002</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.4">
@@ -5063,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="D290">
-        <v>13.953250000000001</v>
+        <v>39.977130000000002</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.4">
@@ -5077,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="D291">
-        <v>13.98654</v>
+        <v>40.039630000000002</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.4">
@@ -5091,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="D292">
-        <v>14.02046</v>
+        <v>40.102690000000003</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.4">
@@ -5105,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="D293">
-        <v>14.05495</v>
+        <v>40.166220000000003</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.4">
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="D294">
-        <v>14.08989</v>
+        <v>40.230170000000001</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.4">
@@ -5133,7 +5133,7 @@
         <v>0</v>
       </c>
       <c r="D295">
-        <v>14.1252</v>
+        <v>40.294449999999998</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.4">
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="D296">
-        <v>14.160780000000001</v>
+        <v>40.359020000000001</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.4">
@@ -5161,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="D297">
-        <v>14.19651</v>
+        <v>40.423819999999999</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.4">
@@ -5175,7 +5175,7 @@
         <v>0</v>
       </c>
       <c r="D298">
-        <v>14.2323</v>
+        <v>40.488779999999998</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.4">
@@ -5189,7 +5189,7 @@
         <v>0</v>
       </c>
       <c r="D299">
-        <v>14.26803</v>
+        <v>40.553789999999999</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.4">
@@ -5203,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="D300">
-        <v>14.303599999999999</v>
+        <v>40.618749999999999</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.4">
@@ -5217,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="D301">
-        <v>14.33892</v>
+        <v>40.683570000000003</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.4">
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="D302">
-        <v>14.373900000000001</v>
+        <v>40.748190000000001</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.4">
@@ -5245,7 +5245,7 @@
         <v>0</v>
       </c>
       <c r="D303">
-        <v>14.408440000000001</v>
+        <v>40.812559999999998</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/data_symbols_TD/08_LTAN06_800km_1213COLD_PY_ALL_HEAT_PY_0p5.xlsx
+++ b/inputs/data_symbols_TD/08_LTAN06_800km_1213COLD_PY_ALL_HEAT_PY_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB651092-641E-490E-BCC8-0A8AEF7DF925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA372AA2-5F27-425C-843E-87F5790D045D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{579DD63A-BB7C-43BE-B9EA-8B3F95FAF2C8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{2CFFFA0E-6D21-4758-AE29-1A32AF677242}"/>
   </bookViews>
   <sheets>
     <sheet name="08_LTAN06_800km_1213COLD_PY_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43E5C071-425E-42A4-AE6B-F97DDC813B8F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6353F9-B92F-453E-8B2F-91C9C9E8D264}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/inputs/data_symbols_TD/08_LTAN06_800km_1213COLD_PY_ALL_HEAT_PY_0p5.xlsx
+++ b/inputs/data_symbols_TD/08_LTAN06_800km_1213COLD_PY_ALL_HEAT_PY_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA372AA2-5F27-425C-843E-87F5790D045D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2067E45F-0A85-4696-8A54-8BA419EFFAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{2CFFFA0E-6D21-4758-AE29-1A32AF677242}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{AAB0FFD5-2C97-4967-88EE-9C8A7D70E8E9}"/>
   </bookViews>
   <sheets>
     <sheet name="08_LTAN06_800km_1213COLD_PY_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6353F9-B92F-453E-8B2F-91C9C9E8D264}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{115DC8F0-4BE0-474A-A17C-23E7B88A3482}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
